--- a/SGC-CKN/Excel/88ed6e7d-1241-478e-9310-f839c6c1fba2_D1-171_D1-171_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/88ed6e7d-1241-478e-9310-f839c6c1fba2_D1-171_D1-171_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t>Số hiệu cọc</t>
+  </si>
+  <si>
+    <t>P1-171</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -1039,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1053,10 +1056,10 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1070,10 +1073,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1087,10 +1090,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1104,10 +1107,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1122,54 +1125,54 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
         <v>-0.67</v>
@@ -1187,24 +1190,24 @@
         <v>0.69</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-0.9</v>
@@ -1222,24 +1225,24 @@
         <v>3.87</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="13">
         <v>-3.8</v>
@@ -1257,24 +1260,24 @@
         <v>4.53</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-7.2</v>
@@ -1292,24 +1295,24 @@
         <v>8.6</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="20">
         <v>-15.8</v>
@@ -1327,24 +1330,24 @@
         <v>5.2</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="23">
         <v>-21</v>
@@ -1362,24 +1365,24 @@
         <v>4.8</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>47</v>
-      </c>
       <c r="E17" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="26">
         <v>-25.8</v>
@@ -1397,24 +1400,24 @@
         <v>0.43</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" s="29">
         <v>-26.16</v>
@@ -1432,12 +1435,12 @@
         <v>2.53</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1543,31 +1546,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1575,10 +1578,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
@@ -1604,10 +1607,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1633,10 +1636,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1662,10 +1665,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1691,10 +1694,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="20">
         <v>1</v>
@@ -1720,10 +1723,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="23">
         <v>1</v>
@@ -1749,10 +1752,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -1778,10 +1781,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1804,13 +1807,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="34">
         <v>8</v>
